--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_m_movinterna_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_m_movinterna_a_2021_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 11:11</t>
+    <t xml:space="preserve">2026-09-18 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_m_movinterna_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_m_movinterna_a_2021_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:08</t>
+    <t xml:space="preserve">2026-09-29 11:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,7 +474,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6.09</v>
+        <v>60.93</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7.74</v>
+        <v>77.39</v>
       </c>
     </row>
     <row r="4">
@@ -496,7 +496,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10.25</v>
+        <v>102.55</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9.62</v>
+        <v>96.17</v>
       </c>
     </row>
     <row r="6">
@@ -518,7 +518,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9.82</v>
+        <v>98.22</v>
       </c>
     </row>
     <row r="7">
@@ -529,7 +529,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10.43</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="8">
@@ -540,7 +540,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5.65</v>
+        <v>56.45</v>
       </c>
     </row>
     <row r="9">
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6.88</v>
+        <v>68.82</v>
       </c>
     </row>
     <row r="10">
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7.97</v>
+        <v>79.69</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +573,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7.79</v>
+        <v>77.91</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7.43</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="13">
@@ -595,7 +595,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7.78</v>
+        <v>77.78</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6.8</v>
+        <v>67.99</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7.97</v>
+        <v>79.74</v>
       </c>
     </row>
     <row r="4">
@@ -727,7 +727,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8.38</v>
+        <v>83.85</v>
       </c>
     </row>
     <row r="5">
@@ -738,7 +738,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8.75</v>
+        <v>87.51</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +749,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8.16</v>
+        <v>81.62</v>
       </c>
     </row>
     <row r="7">
@@ -760,7 +760,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8.39</v>
+        <v>83.91</v>
       </c>
     </row>
     <row r="8">
@@ -771,7 +771,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>8.18</v>
+        <v>81.84</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>9.33</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="10">
@@ -793,7 +793,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11.64</v>
+        <v>116.37</v>
       </c>
     </row>
     <row r="11">
@@ -804,7 +804,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10.72</v>
+        <v>107.21</v>
       </c>
     </row>
     <row r="12">
@@ -815,7 +815,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10.14</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="13">
@@ -826,7 +826,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10.43</v>
+        <v>104.27</v>
       </c>
     </row>
     <row r="14">
@@ -837,7 +837,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5.68</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="15">
@@ -848,7 +848,7 @@
         <v>20</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7.58</v>
+        <v>75.76</v>
       </c>
     </row>
     <row r="16">
@@ -859,7 +859,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>10.24</v>
+        <v>102.36</v>
       </c>
     </row>
     <row r="17">
@@ -870,7 +870,7 @@
         <v>20</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>10.07</v>
+        <v>100.74</v>
       </c>
     </row>
     <row r="18">
@@ -881,7 +881,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>10.01</v>
+        <v>100.07</v>
       </c>
     </row>
     <row r="19">
@@ -892,7 +892,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>10.93</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="20">
@@ -903,7 +903,7 @@
         <v>21</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5.18</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="21">
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7.61</v>
+        <v>76.13</v>
       </c>
     </row>
     <row r="22">
@@ -925,7 +925,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>7.37</v>
+        <v>73.68</v>
       </c>
     </row>
     <row r="23">
@@ -936,7 +936,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6.84</v>
+        <v>68.43</v>
       </c>
     </row>
     <row r="24">
@@ -947,7 +947,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6.9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
@@ -958,7 +958,7 @@
         <v>21</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6.57</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="26">
@@ -969,7 +969,7 @@
         <v>22</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>3.21</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="27">
@@ -980,7 +980,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3.4</v>
+        <v>34.01</v>
       </c>
     </row>
     <row r="28">
@@ -991,7 +991,7 @@
         <v>22</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>4.66</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="29">
@@ -1002,7 +1002,7 @@
         <v>22</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4.42</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="30">
@@ -1013,7 +1013,7 @@
         <v>22</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5.11</v>
+        <v>51.06</v>
       </c>
     </row>
     <row r="31">
@@ -1024,7 +1024,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5.52</v>
+        <v>55.2</v>
       </c>
     </row>
   </sheetData>
